--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,48 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131</v>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="MessageLimiter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,10 +15,8 @@
   <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,13 +28,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -50,9 +37,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -167,72 +153,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -288,7 +216,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +225,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -337,17 +265,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -402,8 +319,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -438,50 +353,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>68</v>
@@ -493,7 +368,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -507,7 +382,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +396,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +410,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,6 +538,132 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>168</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>169</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>171</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>172</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>173</v>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>174</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>175</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>54</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +620,118 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>181</v>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>182</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>183</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>185</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>186</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>187</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>188</v>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>189</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
